--- a/Lista_Invitados_Boda(1).xlsx
+++ b/Lista_Invitados_Boda(1).xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="143">
   <si>
     <t>No.</t>
   </si>
@@ -448,6 +448,9 @@
   </si>
   <si>
     <t>NICOLL PORTILLO</t>
+  </si>
+  <si>
+    <t>OSMAN ROSTRAN</t>
   </si>
 </sst>
 </file>
@@ -790,7 +793,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -2348,6 +2351,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>142</v>
+      </c>
+      <c r="C142">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
